--- a/Team-Data/2014-15/2-1-2014-15.xlsx
+++ b/Team-Data/2014-15/2-1-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>7.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -772,7 +839,7 @@
         <v>1</v>
       </c>
       <c r="AO2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP2" t="n">
         <v>18</v>
@@ -781,7 +848,7 @@
         <v>8</v>
       </c>
       <c r="AR2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS2" t="n">
         <v>14</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -843,46 +910,46 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E3" t="n">
         <v>16</v>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G3" t="n">
-        <v>0.348</v>
+        <v>0.356</v>
       </c>
       <c r="H3" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I3" t="n">
-        <v>39.3</v>
+        <v>39.5</v>
       </c>
       <c r="J3" t="n">
-        <v>87.59999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="K3" t="n">
-        <v>0.448</v>
+        <v>0.45</v>
       </c>
       <c r="L3" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M3" t="n">
         <v>23</v>
       </c>
       <c r="N3" t="n">
-        <v>0.328</v>
+        <v>0.33</v>
       </c>
       <c r="O3" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="P3" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.752</v>
+        <v>0.755</v>
       </c>
       <c r="R3" t="n">
         <v>10.6</v>
@@ -894,7 +961,7 @@
         <v>43.3</v>
       </c>
       <c r="U3" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="V3" t="n">
         <v>14.5</v>
@@ -906,28 +973,28 @@
         <v>4.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA3" t="n">
         <v>18</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.9</v>
+        <v>101.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>-2.2</v>
+        <v>-2</v>
       </c>
       <c r="AD3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AE3" t="n">
         <v>25</v>
       </c>
       <c r="AF3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG3" t="n">
         <v>24</v>
@@ -963,40 +1030,40 @@
         <v>16</v>
       </c>
       <c r="AR3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AS3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU3" t="n">
         <v>5</v>
       </c>
       <c r="AV3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW3" t="n">
         <v>10</v>
       </c>
       <c r="AX3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AZ3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
         <v>30</v>
       </c>
       <c r="BB3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BC3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1194,7 @@
         <v>18</v>
       </c>
       <c r="AL4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM4" t="n">
         <v>19</v>
@@ -1148,7 +1215,7 @@
         <v>26</v>
       </c>
       <c r="AS4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT4" t="n">
         <v>23</v>
@@ -1157,7 +1224,7 @@
         <v>22</v>
       </c>
       <c r="AV4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW4" t="n">
         <v>18</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -1285,10 +1352,10 @@
         <v>-2.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF5" t="n">
         <v>18</v>
@@ -1333,7 +1400,7 @@
         <v>7</v>
       </c>
       <c r="AT5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU5" t="n">
         <v>26</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
         <v>10</v>
@@ -1530,7 +1597,7 @@
         <v>1</v>
       </c>
       <c r="AY6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ6" t="n">
         <v>3</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1716,10 @@
         <v>2.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF7" t="n">
         <v>12</v>
@@ -1664,7 +1731,7 @@
         <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ7" t="n">
         <v>20</v>
@@ -1679,13 +1746,13 @@
         <v>10</v>
       </c>
       <c r="AN7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO7" t="n">
         <v>6</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ7" t="n">
         <v>15</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E8" t="n">
         <v>32</v>
       </c>
       <c r="F8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" t="n">
-        <v>0.667</v>
+        <v>0.653</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
@@ -1771,7 +1838,7 @@
         <v>40.3</v>
       </c>
       <c r="J8" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="K8" t="n">
         <v>0.471</v>
@@ -1780,7 +1847,7 @@
         <v>9.5</v>
       </c>
       <c r="M8" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="N8" t="n">
         <v>0.36</v>
@@ -1789,25 +1856,25 @@
         <v>16.9</v>
       </c>
       <c r="P8" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.758</v>
+        <v>0.759</v>
       </c>
       <c r="R8" t="n">
         <v>10.6</v>
       </c>
       <c r="S8" t="n">
-        <v>31.6</v>
+        <v>31.4</v>
       </c>
       <c r="T8" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U8" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="V8" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="W8" t="n">
         <v>8.1</v>
@@ -1822,34 +1889,34 @@
         <v>19.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>107</v>
+        <v>106.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK8" t="n">
         <v>5</v>
@@ -1861,7 +1928,7 @@
         <v>5</v>
       </c>
       <c r="AN8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO8" t="n">
         <v>19</v>
@@ -1870,13 +1937,13 @@
         <v>20</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT8" t="n">
         <v>20</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-3.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE9" t="n">
         <v>19</v>
@@ -2025,7 +2092,7 @@
         <v>19</v>
       </c>
       <c r="AH9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI9" t="n">
         <v>14</v>
@@ -2049,7 +2116,7 @@
         <v>9</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ9" t="n">
         <v>25</v>
@@ -2064,7 +2131,7 @@
         <v>5</v>
       </c>
       <c r="AU9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV9" t="n">
         <v>11</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -2195,19 +2262,19 @@
         <v>-2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE10" t="n">
         <v>20</v>
       </c>
       <c r="AF10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG10" t="n">
         <v>21</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
         <v>23</v>
@@ -2270,7 +2337,7 @@
         <v>21</v>
       </c>
       <c r="BC10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>11.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -2481,55 +2548,55 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" t="n">
         <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>0.681</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="J12" t="n">
-        <v>83.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L12" t="n">
         <v>11.8</v>
       </c>
       <c r="M12" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0.35</v>
+        <v>0.352</v>
       </c>
       <c r="O12" t="n">
-        <v>17.3</v>
+        <v>17.6</v>
       </c>
       <c r="P12" t="n">
-        <v>24</v>
+        <v>24.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.72</v>
+        <v>0.719</v>
       </c>
       <c r="R12" t="n">
         <v>12</v>
       </c>
       <c r="S12" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T12" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="U12" t="n">
         <v>21.3</v>
@@ -2538,46 +2605,46 @@
         <v>17.3</v>
       </c>
       <c r="W12" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X12" t="n">
         <v>4.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>102.6</v>
+        <v>102.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AF12" t="n">
         <v>4</v>
       </c>
       <c r="AG12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AH12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI12" t="n">
         <v>21</v>
       </c>
       <c r="AJ12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AK12" t="n">
         <v>21</v>
@@ -2589,25 +2656,25 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AP12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
       </c>
       <c r="AR12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS12" t="n">
         <v>22</v>
       </c>
       <c r="AT12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU12" t="n">
         <v>16</v>
@@ -2619,22 +2686,22 @@
         <v>1</v>
       </c>
       <c r="AX12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BB12" t="n">
         <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE13" t="n">
         <v>22</v>
@@ -2759,7 +2826,7 @@
         <v>25</v>
       </c>
       <c r="AJ13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK13" t="n">
         <v>27</v>
@@ -2795,7 +2862,7 @@
         <v>20</v>
       </c>
       <c r="AV13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW13" t="n">
         <v>29</v>
@@ -2807,7 +2874,7 @@
         <v>16</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA13" t="n">
         <v>8</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>7.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE14" t="n">
         <v>4</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -3045,25 +3112,25 @@
         <v>37.3</v>
       </c>
       <c r="J15" t="n">
-        <v>85.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K15" t="n">
         <v>0.436</v>
       </c>
       <c r="L15" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M15" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="N15" t="n">
-        <v>0.348</v>
+        <v>0.346</v>
       </c>
       <c r="O15" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="P15" t="n">
-        <v>24.3</v>
+        <v>24.7</v>
       </c>
       <c r="Q15" t="n">
         <v>0.747</v>
@@ -3072,10 +3139,10 @@
         <v>11.5</v>
       </c>
       <c r="S15" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="T15" t="n">
-        <v>43.5</v>
+        <v>43.3</v>
       </c>
       <c r="U15" t="n">
         <v>20.5</v>
@@ -3093,19 +3160,19 @@
         <v>4.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>21</v>
+        <v>21.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.40000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.4</v>
+        <v>-6.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3120,10 +3187,10 @@
         <v>11</v>
       </c>
       <c r="AI15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK15" t="n">
         <v>24</v>
@@ -3135,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="AN15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AQ15" t="n">
         <v>20</v>
@@ -3150,10 +3217,10 @@
         <v>10</v>
       </c>
       <c r="AS15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AU15" t="n">
         <v>23</v>
@@ -3165,13 +3232,13 @@
         <v>19</v>
       </c>
       <c r="AX15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY15" t="n">
         <v>9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BA15" t="n">
         <v>19</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>5.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3305,7 +3372,7 @@
         <v>8</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK16" t="n">
         <v>7</v>
@@ -3317,10 +3384,10 @@
         <v>28</v>
       </c>
       <c r="AN16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP16" t="n">
         <v>11</v>
@@ -3332,7 +3399,7 @@
         <v>20</v>
       </c>
       <c r="AS16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT16" t="n">
         <v>16</v>
@@ -3341,7 +3408,7 @@
         <v>10</v>
       </c>
       <c r="AV16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW16" t="n">
         <v>8</v>
@@ -3359,7 +3426,7 @@
         <v>11</v>
       </c>
       <c r="BB16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC16" t="n">
         <v>6</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F17" t="n">
         <v>26</v>
       </c>
       <c r="G17" t="n">
-        <v>0.447</v>
+        <v>0.435</v>
       </c>
       <c r="H17" t="n">
         <v>48</v>
@@ -3409,25 +3476,25 @@
         <v>34.1</v>
       </c>
       <c r="J17" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.454</v>
+        <v>0.455</v>
       </c>
       <c r="L17" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M17" t="n">
         <v>20.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.337</v>
+        <v>0.34</v>
       </c>
       <c r="O17" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="P17" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="Q17" t="n">
         <v>0.74</v>
@@ -3436,22 +3503,22 @@
         <v>8.5</v>
       </c>
       <c r="S17" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="T17" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="U17" t="n">
         <v>19.9</v>
       </c>
       <c r="V17" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W17" t="n">
         <v>8</v>
       </c>
       <c r="X17" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y17" t="n">
         <v>4.3</v>
@@ -3463,13 +3530,13 @@
         <v>20.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>92.40000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>-3.5</v>
+        <v>-3.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3490,19 +3557,19 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM17" t="n">
         <v>20</v>
       </c>
       <c r="AN17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
         <v>13</v>
@@ -3511,7 +3578,7 @@
         <v>23</v>
       </c>
       <c r="AR17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS17" t="n">
         <v>29</v>
@@ -3523,13 +3590,13 @@
         <v>29</v>
       </c>
       <c r="AV17" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AW17" t="n">
         <v>11</v>
       </c>
       <c r="AX17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AY17" t="n">
         <v>8</v>
@@ -3538,7 +3605,7 @@
         <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB17" t="n">
         <v>29</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>1.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE18" t="n">
         <v>14</v>
@@ -3717,7 +3784,7 @@
         <v>11</v>
       </c>
       <c r="AZ18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA18" t="n">
         <v>23</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-9.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE19" t="n">
         <v>30</v>
@@ -3845,7 +3912,7 @@
         <v>30</v>
       </c>
       <c r="AH19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
         <v>20</v>
@@ -3863,7 +3930,7 @@
         <v>30</v>
       </c>
       <c r="AN19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO19" t="n">
         <v>5</v>
@@ -3893,7 +3960,7 @@
         <v>7</v>
       </c>
       <c r="AX19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY19" t="n">
         <v>27</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F20" t="n">
         <v>22</v>
       </c>
       <c r="G20" t="n">
-        <v>0.522</v>
+        <v>0.532</v>
       </c>
       <c r="H20" t="n">
         <v>48.2</v>
@@ -3955,76 +4022,76 @@
         <v>38.2</v>
       </c>
       <c r="J20" t="n">
-        <v>83.5</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.457</v>
+        <v>0.455</v>
       </c>
       <c r="L20" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M20" t="n">
         <v>18.9</v>
       </c>
       <c r="N20" t="n">
-        <v>0.348</v>
+        <v>0.346</v>
       </c>
       <c r="O20" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="P20" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.766</v>
+        <v>0.758</v>
       </c>
       <c r="R20" t="n">
-        <v>11.8</v>
+        <v>12.1</v>
       </c>
       <c r="S20" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="T20" t="n">
-        <v>43.8</v>
+        <v>44.2</v>
       </c>
       <c r="U20" t="n">
         <v>21.2</v>
       </c>
       <c r="V20" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="W20" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X20" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="AB20" t="n">
         <v>100.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AE20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF20" t="n">
         <v>14</v>
       </c>
       <c r="AG20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH20" t="n">
         <v>22</v>
@@ -4033,43 +4100,43 @@
         <v>10</v>
       </c>
       <c r="AJ20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AK20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM20" t="n">
         <v>25</v>
       </c>
       <c r="AN20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AP20" t="n">
         <v>17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AR20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AS20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT20" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AU20" t="n">
         <v>19</v>
       </c>
       <c r="AV20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW20" t="n">
         <v>23</v>
@@ -4090,7 +4157,7 @@
         <v>16</v>
       </c>
       <c r="BC20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -4119,22 +4186,22 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F21" t="n">
         <v>38</v>
       </c>
       <c r="G21" t="n">
-        <v>0.208</v>
+        <v>0.191</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J21" t="n">
         <v>81.90000000000001</v>
@@ -4143,43 +4210,43 @@
         <v>0.439</v>
       </c>
       <c r="L21" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M21" t="n">
         <v>20.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0.361</v>
+        <v>0.359</v>
       </c>
       <c r="O21" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="P21" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.765</v>
+        <v>0.768</v>
       </c>
       <c r="R21" t="n">
         <v>10.6</v>
       </c>
       <c r="S21" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T21" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="U21" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V21" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W21" t="n">
         <v>7.2</v>
       </c>
       <c r="X21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y21" t="n">
         <v>4.1</v>
@@ -4188,25 +4255,25 @@
         <v>22.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AB21" t="n">
         <v>92.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>-7.5</v>
+        <v>-7.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="AE21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF21" t="n">
         <v>28</v>
       </c>
       <c r="AG21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH21" t="n">
         <v>19</v>
@@ -4227,7 +4294,7 @@
         <v>21</v>
       </c>
       <c r="AN21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4236,10 +4303,10 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS21" t="n">
         <v>28</v>
@@ -4248,10 +4315,10 @@
         <v>29</v>
       </c>
       <c r="AU21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AW21" t="n">
         <v>22</v>
@@ -4266,7 +4333,7 @@
         <v>25</v>
       </c>
       <c r="BA21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB21" t="n">
         <v>28</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>0.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE22" t="n">
         <v>16</v>
@@ -4394,7 +4461,7 @@
         <v>15</v>
       </c>
       <c r="AI22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ22" t="n">
         <v>10</v>
@@ -4412,7 +4479,7 @@
         <v>27</v>
       </c>
       <c r="AO22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP22" t="n">
         <v>14</v>
@@ -4421,7 +4488,7 @@
         <v>22</v>
       </c>
       <c r="AR22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS22" t="n">
         <v>3</v>
@@ -4445,7 +4512,7 @@
         <v>13</v>
       </c>
       <c r="AZ22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA22" t="n">
         <v>22</v>
@@ -4454,7 +4521,7 @@
         <v>19</v>
       </c>
       <c r="BC22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -4483,40 +4550,40 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E23" t="n">
         <v>15</v>
       </c>
       <c r="F23" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G23" t="n">
-        <v>0.306</v>
+        <v>0.3</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J23" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.457</v>
+        <v>0.455</v>
       </c>
       <c r="L23" t="n">
         <v>7</v>
       </c>
       <c r="M23" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="N23" t="n">
         <v>0.362</v>
       </c>
       <c r="O23" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="P23" t="n">
         <v>19.8</v>
@@ -4525,13 +4592,13 @@
         <v>0.731</v>
       </c>
       <c r="R23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="S23" t="n">
-        <v>31.5</v>
+        <v>31.7</v>
       </c>
       <c r="T23" t="n">
-        <v>40.3</v>
+        <v>40.6</v>
       </c>
       <c r="U23" t="n">
         <v>20.3</v>
@@ -4543,22 +4610,22 @@
         <v>7.5</v>
       </c>
       <c r="X23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA23" t="n">
         <v>18.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>96</v>
+        <v>95.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6.1</v>
+        <v>-6.3</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4567,25 +4634,25 @@
         <v>26</v>
       </c>
       <c r="AF23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG23" t="n">
         <v>26</v>
       </c>
       <c r="AH23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ23" t="n">
         <v>24</v>
       </c>
       <c r="AK23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM23" t="n">
         <v>22</v>
@@ -4606,13 +4673,13 @@
         <v>28</v>
       </c>
       <c r="AS23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT23" t="n">
         <v>28</v>
       </c>
       <c r="AU23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV23" t="n">
         <v>20</v>
@@ -4624,16 +4691,16 @@
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
         <v>22</v>
       </c>
       <c r="BA23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC23" t="n">
         <v>26</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-11.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4809,10 +4876,10 @@
         <v>23</v>
       </c>
       <c r="AZ24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>1.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -4955,7 +5022,7 @@
         <v>3</v>
       </c>
       <c r="AN25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO25" t="n">
         <v>18</v>
@@ -4970,7 +5037,7 @@
         <v>16</v>
       </c>
       <c r="AS25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT25" t="n">
         <v>18</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -5107,10 +5174,10 @@
         <v>5.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF26" t="n">
         <v>7</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5377,7 @@
         <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL27" t="n">
         <v>29</v>
@@ -5361,7 +5428,7 @@
         <v>1</v>
       </c>
       <c r="BB27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC27" t="n">
         <v>22</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -5393,73 +5460,73 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F28" t="n">
         <v>18</v>
       </c>
       <c r="G28" t="n">
-        <v>0.617</v>
+        <v>0.625</v>
       </c>
       <c r="H28" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="I28" t="n">
         <v>37.8</v>
       </c>
       <c r="J28" t="n">
-        <v>83.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.454</v>
+        <v>0.456</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="O28" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="P28" t="n">
         <v>22.4</v>
       </c>
-      <c r="N28" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="O28" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="P28" t="n">
-        <v>22.5</v>
-      </c>
       <c r="Q28" t="n">
-        <v>0.765</v>
+        <v>0.766</v>
       </c>
       <c r="R28" t="n">
         <v>9.9</v>
       </c>
       <c r="S28" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="T28" t="n">
-        <v>43.9</v>
+        <v>43.7</v>
       </c>
       <c r="U28" t="n">
         <v>24.1</v>
       </c>
       <c r="V28" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W28" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA28" t="n">
         <v>20.2</v>
@@ -5468,13 +5535,13 @@
         <v>101</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF28" t="n">
         <v>10</v>
@@ -5483,7 +5550,7 @@
         <v>10</v>
       </c>
       <c r="AH28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI28" t="n">
         <v>13</v>
@@ -5492,7 +5559,7 @@
         <v>18</v>
       </c>
       <c r="AK28" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AL28" t="n">
         <v>11</v>
@@ -5504,7 +5571,7 @@
         <v>7</v>
       </c>
       <c r="AO28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP28" t="n">
         <v>19</v>
@@ -5519,13 +5586,13 @@
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW28" t="n">
         <v>14</v>
@@ -5543,10 +5610,10 @@
         <v>18</v>
       </c>
       <c r="BB28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>5.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
         <v>4</v>
@@ -5683,7 +5750,7 @@
         <v>7</v>
       </c>
       <c r="AN29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO29" t="n">
         <v>3</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -5835,13 +5902,13 @@
         <v>-2.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE30" t="n">
         <v>22</v>
       </c>
       <c r="AF30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG30" t="n">
         <v>23</v>
@@ -5868,7 +5935,7 @@
         <v>20</v>
       </c>
       <c r="AO30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP30" t="n">
         <v>16</v>
@@ -5886,7 +5953,7 @@
         <v>17</v>
       </c>
       <c r="AU30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV30" t="n">
         <v>26</v>
@@ -5907,7 +5974,7 @@
         <v>24</v>
       </c>
       <c r="BB30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC30" t="n">
         <v>21</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
@@ -6017,13 +6084,13 @@
         <v>2</v>
       </c>
       <c r="AD31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE31" t="n">
         <v>9</v>
       </c>
       <c r="AF31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG31" t="n">
         <v>9</v>
@@ -6083,7 +6150,7 @@
         <v>7</v>
       </c>
       <c r="AZ31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA31" t="n">
         <v>17</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-1-2014-15</t>
+          <t>2015-02-01</t>
         </is>
       </c>
     </row>
